--- a/Structure.xlsx
+++ b/Structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\MyBudget-Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50422402-A710-4373-BBBB-860BD9200CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E37D0F4-C505-4C8B-99BD-ED2F5A5D5993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A773E5D0-AB37-46BE-88A7-52208892E9A5}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>Bank Balance</t>
   </si>
@@ -76,6 +76,39 @@
   </si>
   <si>
     <t>Datetime</t>
+  </si>
+  <si>
+    <t>Controllers</t>
+  </si>
+  <si>
+    <t>BankBalanceController</t>
+  </si>
+  <si>
+    <t>ExpensesController</t>
+  </si>
+  <si>
+    <t>DashboardController</t>
+  </si>
+  <si>
+    <t>Handles setting/updating the balance</t>
+  </si>
+  <si>
+    <t>Handles add/edit/delete expenses</t>
+  </si>
+  <si>
+    <t>Shows summary: total expenses, remaining balance, etc</t>
+  </si>
+  <si>
+    <t>Set Balance View</t>
+  </si>
+  <si>
+    <t>Add/View Expense View</t>
+  </si>
+  <si>
+    <t>Summary Dashboard View</t>
+  </si>
+  <si>
+    <t>View</t>
   </si>
 </sst>
 </file>
@@ -142,14 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,27 +495,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAA735E-E2A9-4922-A6A8-44BFD06EA29A}">
-  <dimension ref="B2:D11"/>
+  <dimension ref="B2:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
@@ -492,7 +542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
@@ -500,53 +550,86 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C8" s="5" t="s">
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="5" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C10" s="5" t="s">
+      <c r="F9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C11" s="5" t="s">
+      <c r="F10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="F11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Structure.xlsx
+++ b/Structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\MyBudget-Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E37D0F4-C505-4C8B-99BD-ED2F5A5D5993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACAA390-496B-4557-90B1-7E43E677546F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A773E5D0-AB37-46BE-88A7-52208892E9A5}"/>
   </bookViews>

--- a/Structure.xlsx
+++ b/Structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\MyBudget-Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACAA390-496B-4557-90B1-7E43E677546F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75DA789-A446-438F-8E72-3F930EF50DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A773E5D0-AB37-46BE-88A7-52208892E9A5}"/>
   </bookViews>
